--- a/output/legajos_maestro.xlsx
+++ b/output/legajos_maestro.xlsx
@@ -553,7 +553,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Juan Perez</t>
+          <t>Perez</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
@@ -614,12 +614,12 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Mar del Plata</t>
+          <t>MAR DEL PLATA</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Pablo Gonzalez</t>
+          <t>Gonzalez</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
@@ -680,7 +680,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>CORDOBA</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">

--- a/output/legajos_maestro.xlsx
+++ b/output/legajos_maestro.xlsx
@@ -557,13 +557,13 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>2707521.33</v>
+        <v>2722000</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>2707521.33</v>
+        <v>2722000</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>488.04</v>
@@ -576,7 +576,7 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>27.3%</t>
+          <t>27.2%</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -689,13 +689,13 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1702509.5</v>
+        <v>1771354.5</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>1702509.5</v>
+        <v>1771354.5</v>
       </c>
       <c r="G4" t="n">
         <v>523.47</v>
@@ -708,7 +708,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>43.2%</t>
+          <t>41.5%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -734,7 +734,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>credito no aprobado — Relación cuota/ingreso de 43.2% supera el límite de 40%; LTV de 40.5% supera el límite de 35%</t>
+          <t>credito no aprobado — Relación cuota/ingreso de 41.5% supera el límite de 40%; LTV de 40.5% supera el límite de 35%</t>
         </is>
       </c>
     </row>

--- a/output/legajos_maestro.xlsx
+++ b/output/legajos_maestro.xlsx
@@ -559,9 +559,7 @@
       <c r="D2" s="2" t="n">
         <v>2722000</v>
       </c>
-      <c r="E2" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E2" s="2" t="n"/>
       <c r="F2" s="2" t="n">
         <v>2722000</v>
       </c>
@@ -625,9 +623,7 @@
       <c r="D3" s="2" t="n">
         <v>2709944.17</v>
       </c>
-      <c r="E3" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E3" s="2" t="n"/>
       <c r="F3" s="2" t="n">
         <v>2709944.17</v>
       </c>
@@ -690,9 +686,6 @@
       </c>
       <c r="D4" t="n">
         <v>1771354.5</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
       </c>
       <c r="F4" t="n">
         <v>1771354.5</v>
